--- a/data/trans_orig/ProblemasDormirP33b-Clase-trans_orig.xlsx
+++ b/data/trans_orig/ProblemasDormirP33b-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con problemas para dormir a diario en 2023</t>
+          <t>Población con problemas para dormir a diario en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52339</t>
+          <t>54294</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83670</t>
+          <t>84428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59915</t>
+          <t>59449</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87181</t>
+          <t>86603</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119481</t>
+          <t>119671</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>160212</t>
+          <t>160855</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>421542</t>
+          <t>420784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452873</t>
+          <t>450918</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>360286</t>
+          <t>360864</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>387552</t>
+          <t>388018</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>792467</t>
+          <t>791824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>833198</t>
+          <t>833008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36708</t>
+          <t>37190</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62781</t>
+          <t>64422</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54344</t>
+          <t>53212</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79453</t>
+          <t>79059</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99146</t>
+          <t>98558</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>135712</t>
+          <t>133440</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>389432</t>
+          <t>387791</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415505</t>
+          <t>415023</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>303127</t>
+          <t>303521</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328236</t>
+          <t>329368</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>699081</t>
+          <t>701353</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>735647</t>
+          <t>736235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,19%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22418</t>
+          <t>26220</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110008</t>
+          <t>112405</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36116</t>
+          <t>35725</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53572</t>
+          <t>53115</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46901</t>
+          <t>48360</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162411</t>
+          <t>161837</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>558256</t>
+          <t>555859</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>645846</t>
+          <t>642044</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113339</t>
+          <t>113796</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130795</t>
+          <t>131186</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>672764</t>
+          <t>673338</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>786815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>130295</t>
+          <t>128889</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>176041</t>
+          <t>176854</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65067</t>
+          <t>75251</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>179460</t>
+          <t>178144</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>204343</t>
+          <t>187563</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>331606</t>
+          <t>330001</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>858778</t>
+          <t>857965</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>904524</t>
+          <t>905930</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>798634</t>
+          <t>799950</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>913027</t>
+          <t>902843</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1681306</t>
+          <t>1682911</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1808569</t>
+          <t>1825349</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44592</t>
+          <t>44905</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70639</t>
+          <t>72282</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151303</t>
+          <t>155411</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>236837</t>
+          <t>239591</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>212454</t>
+          <t>208810</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>291100</t>
+          <t>289986</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>404407</t>
+          <t>402764</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>430454</t>
+          <t>430141</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>604498</t>
+          <t>601744</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>690032</t>
+          <t>685924</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1025281</t>
+          <t>1026395</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1103927</t>
+          <t>1107571</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>10079</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39731</t>
+          <t>38090</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>145563</t>
+          <t>145970</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>181825</t>
+          <t>183871</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>163057</t>
+          <t>162416</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>208218</t>
+          <t>209537</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200776</t>
+          <t>202417</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230727</t>
+          <t>230428</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>579546</t>
+          <t>577500</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>615808</t>
+          <t>615401</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>793660</t>
+          <t>792341</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>838821</t>
+          <t>839462</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,79%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>319437</t>
+          <t>325627</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>457600</t>
+          <t>461645</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>558339</t>
+          <t>554819</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>752079</t>
+          <t>751014</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>955790</t>
+          <t>959732</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1192808</t>
+          <t>1184102</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2918460</t>
+          <t>2914415</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3056623</t>
+          <t>3050433</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2825679</t>
+          <t>2826744</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3019419</t>
+          <t>3022939</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5761010</t>
+          <t>5769716</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5998028</t>
+          <t>5994086</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,2%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ProblemasDormirP33b-Clase-trans_orig.xlsx
+++ b/data/trans_orig/ProblemasDormirP33b-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>66917</t>
+          <t>73185</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54294</t>
+          <t>58803</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84428</t>
+          <t>91542</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>72459</t>
+          <t>81374</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59449</t>
+          <t>68511</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86603</t>
+          <t>97969</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>139376</t>
+          <t>154560</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119671</t>
+          <t>134833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>160855</t>
+          <t>178474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>438295</t>
+          <t>477433</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>420784</t>
+          <t>459076</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>450918</t>
+          <t>491815</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>375008</t>
+          <t>407037</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>360864</t>
+          <t>390442</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>388018</t>
+          <t>419900</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>813303</t>
+          <t>884469</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>791824</t>
+          <t>860555</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>833008</t>
+          <t>904196</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49235</t>
+          <t>53146</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37190</t>
+          <t>40982</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64422</t>
+          <t>68428</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66261</t>
+          <t>74179</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53212</t>
+          <t>62318</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79059</t>
+          <t>90337</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>115496</t>
+          <t>127325</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98558</t>
+          <t>109413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133440</t>
+          <t>147495</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>402978</t>
+          <t>430066</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>387791</t>
+          <t>414784</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415023</t>
+          <t>442230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>316319</t>
+          <t>348964</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>303521</t>
+          <t>332806</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>329368</t>
+          <t>360825</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>719297</t>
+          <t>779030</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>701353</t>
+          <t>758860</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736235</t>
+          <t>796942</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,93%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>66338</t>
+          <t>72279</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26220</t>
+          <t>57729</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>112405</t>
+          <t>89941</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44268</t>
+          <t>49880</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35725</t>
+          <t>39760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53115</t>
+          <t>59497</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>110606</t>
+          <t>122159</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48360</t>
+          <t>104332</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161837</t>
+          <t>140161</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>601926</t>
+          <t>399333</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>555859</t>
+          <t>381671</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>642044</t>
+          <t>413883</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>122643</t>
+          <t>137617</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113796</t>
+          <t>128000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131186</t>
+          <t>147737</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>724569</t>
+          <t>536950</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>673338</t>
+          <t>518948</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>786815</t>
+          <t>554777</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>151724</t>
+          <t>168533</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>128889</t>
+          <t>145621</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>176854</t>
+          <t>195195</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>134541</t>
+          <t>152795</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75251</t>
+          <t>133711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178144</t>
+          <t>172610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>286265</t>
+          <t>321328</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>187563</t>
+          <t>294069</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>330001</t>
+          <t>352600</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>883095</t>
+          <t>963310</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>857965</t>
+          <t>936648</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>905930</t>
+          <t>986222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>843553</t>
+          <t>708416</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>799950</t>
+          <t>688601</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>902843</t>
+          <t>727500</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1726647</t>
+          <t>1671726</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1682911</t>
+          <t>1640454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1825349</t>
+          <t>1698985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>56260</t>
+          <t>65106</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44905</t>
+          <t>51788</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72282</t>
+          <t>81975</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>203675</t>
+          <t>224010</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>155411</t>
+          <t>204307</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>239591</t>
+          <t>244903</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>259935</t>
+          <t>289116</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>208810</t>
+          <t>263875</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>289986</t>
+          <t>318721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>418786</t>
+          <t>502858</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>402764</t>
+          <t>485989</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>430141</t>
+          <t>516176</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>637660</t>
+          <t>606840</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>601744</t>
+          <t>585947</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>685924</t>
+          <t>626543</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1056446</t>
+          <t>1109698</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1026395</t>
+          <t>1080093</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1107571</t>
+          <t>1134939</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>81,14%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20644</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38090</t>
+          <t>35703</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>164194</t>
+          <t>180640</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>145970</t>
+          <t>158553</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>183871</t>
+          <t>199789</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>184838</t>
+          <t>199387</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>162416</t>
+          <t>177396</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>209537</t>
+          <t>226250</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>219863</t>
+          <t>218481</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202417</t>
+          <t>201525</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230428</t>
+          <t>227142</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>597177</t>
+          <t>663641</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>577500</t>
+          <t>644492</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>615401</t>
+          <t>685728</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>817040</t>
+          <t>882122</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>792341</t>
+          <t>855259</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>839462</t>
+          <t>904113</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>411117</t>
+          <t>450996</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>325627</t>
+          <t>413837</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>461645</t>
+          <t>496393</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>685397</t>
+          <t>762878</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>554819</t>
+          <t>720895</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>751014</t>
+          <t>804732</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1096515</t>
+          <t>1213874</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>959732</t>
+          <t>1150470</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1184102</t>
+          <t>1272761</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2964943</t>
+          <t>2991480</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2914415</t>
+          <t>2946083</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3050433</t>
+          <t>3028639</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2892361</t>
+          <t>2872515</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2826744</t>
+          <t>2830661</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3022939</t>
+          <t>2914498</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5857303</t>
+          <t>5863995</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5769716</t>
+          <t>5805108</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5994086</t>
+          <t>5927399</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
